--- a/MIP_RULE/results/random_best_piece_details.xlsx
+++ b/MIP_RULE/results/random_best_piece_details.xlsx
@@ -530,22 +530,22 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>7.7</v>
+        <v>3.05</v>
       </c>
       <c r="J2" t="n">
-        <v>7.7</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>13.55</v>
+        <v>8.9</v>
       </c>
       <c r="M2" t="n">
-        <v>15.39</v>
+        <v>10.74</v>
       </c>
       <c r="N2" t="n">
-        <v>13.55</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3">
@@ -674,22 +674,22 @@
         <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>21.15</v>
+        <v>16.5</v>
       </c>
       <c r="J5" t="n">
-        <v>21.15</v>
+        <v>16.5</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>27.66</v>
+        <v>23.01</v>
       </c>
       <c r="M5" t="n">
-        <v>30.18</v>
+        <v>25.53</v>
       </c>
       <c r="N5" t="n">
-        <v>27.66</v>
+        <v>23.01</v>
       </c>
     </row>
     <row r="6">
@@ -770,22 +770,22 @@
         <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>31.15</v>
+        <v>26.5</v>
       </c>
       <c r="J7" t="n">
-        <v>31.15</v>
+        <v>26.5</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>37.66</v>
+        <v>33.01</v>
       </c>
       <c r="M7" t="n">
-        <v>40.18</v>
+        <v>35.53</v>
       </c>
       <c r="N7" t="n">
-        <v>37.66</v>
+        <v>33.01</v>
       </c>
     </row>
     <row r="8">
@@ -818,22 +818,22 @@
         <v>30</v>
       </c>
       <c r="I8" t="n">
-        <v>39.25</v>
+        <v>34.6</v>
       </c>
       <c r="J8" t="n">
-        <v>39.25</v>
+        <v>34.6</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>44.59</v>
+        <v>39.94</v>
       </c>
       <c r="M8" t="n">
-        <v>45.92</v>
+        <v>41.27</v>
       </c>
       <c r="N8" t="n">
-        <v>44.59</v>
+        <v>39.94</v>
       </c>
     </row>
     <row r="9">
@@ -1058,22 +1058,22 @@
         <v>55</v>
       </c>
       <c r="I13" t="n">
-        <v>62.7</v>
+        <v>58.05</v>
       </c>
       <c r="J13" t="n">
-        <v>62.7</v>
+        <v>58.05</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>69.21000000000001</v>
+        <v>64.56</v>
       </c>
       <c r="M13" t="n">
-        <v>71.73</v>
+        <v>67.08</v>
       </c>
       <c r="N13" t="n">
-        <v>69.21000000000001</v>
+        <v>64.56</v>
       </c>
     </row>
     <row r="14">
@@ -1154,22 +1154,22 @@
         <v>65</v>
       </c>
       <c r="I15" t="n">
-        <v>71.15000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="J15" t="n">
-        <v>71.15000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>77.46000000000001</v>
+        <v>72.81</v>
       </c>
       <c r="M15" t="n">
-        <v>79.78</v>
+        <v>75.13</v>
       </c>
       <c r="N15" t="n">
-        <v>77.46000000000001</v>
+        <v>72.81</v>
       </c>
     </row>
     <row r="16">
@@ -1394,22 +1394,22 @@
         <v>90</v>
       </c>
       <c r="I20" t="n">
-        <v>99.25</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>99.25</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>105.1</v>
+        <v>100.45</v>
       </c>
       <c r="M20" t="n">
-        <v>106.94</v>
+        <v>102.29</v>
       </c>
       <c r="N20" t="n">
-        <v>105.1</v>
+        <v>100.45</v>
       </c>
     </row>
     <row r="21">
@@ -1682,22 +1682,22 @@
         <v>120</v>
       </c>
       <c r="I26" t="n">
-        <v>127.7</v>
+        <v>123.05</v>
       </c>
       <c r="J26" t="n">
-        <v>127.7</v>
+        <v>123.05</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>133.55</v>
+        <v>128.9</v>
       </c>
       <c r="M26" t="n">
-        <v>135.39</v>
+        <v>130.74</v>
       </c>
       <c r="N26" t="n">
-        <v>133.55</v>
+        <v>128.9</v>
       </c>
     </row>
     <row r="27">
@@ -1730,22 +1730,22 @@
         <v>125</v>
       </c>
       <c r="I27" t="n">
-        <v>131.15</v>
+        <v>126.5</v>
       </c>
       <c r="J27" t="n">
-        <v>131.15</v>
+        <v>126.5</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>137.46</v>
+        <v>132.81</v>
       </c>
       <c r="M27" t="n">
-        <v>139.78</v>
+        <v>135.13</v>
       </c>
       <c r="N27" t="n">
-        <v>137.46</v>
+        <v>132.81</v>
       </c>
     </row>
     <row r="28">
@@ -1922,22 +1922,22 @@
         <v>145</v>
       </c>
       <c r="I31" t="n">
-        <v>151.15</v>
+        <v>146.5</v>
       </c>
       <c r="J31" t="n">
-        <v>151.15</v>
+        <v>146.5</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>157</v>
+        <v>152.35</v>
       </c>
       <c r="M31" t="n">
-        <v>158.84</v>
+        <v>154.19</v>
       </c>
       <c r="N31" t="n">
-        <v>164.6899999999901</v>
+        <v>160.0399999999901</v>
       </c>
     </row>
     <row r="32">
@@ -1970,22 +1970,22 @@
         <v>150</v>
       </c>
       <c r="I32" t="n">
-        <v>156.15</v>
+        <v>151.5</v>
       </c>
       <c r="J32" t="n">
-        <v>158.8399999999901</v>
+        <v>154.1899999999901</v>
       </c>
       <c r="K32" t="n">
         <v>2.689999999990107</v>
       </c>
       <c r="L32" t="n">
-        <v>164.6899999999901</v>
+        <v>160.0399999999901</v>
       </c>
       <c r="M32" t="n">
-        <v>166.5299999999901</v>
+        <v>161.8799999999901</v>
       </c>
       <c r="N32" t="n">
-        <v>164.6899999999901</v>
+        <v>160.0399999999901</v>
       </c>
     </row>
     <row r="33">
@@ -2258,22 +2258,22 @@
         <v>180</v>
       </c>
       <c r="I38" t="n">
-        <v>187.7</v>
+        <v>183.05</v>
       </c>
       <c r="J38" t="n">
-        <v>187.7</v>
+        <v>183.05</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>193.04</v>
+        <v>188.39</v>
       </c>
       <c r="M38" t="n">
-        <v>194.37</v>
+        <v>189.72</v>
       </c>
       <c r="N38" t="n">
-        <v>193.04</v>
+        <v>188.39</v>
       </c>
     </row>
     <row r="39">
@@ -2306,22 +2306,22 @@
         <v>185</v>
       </c>
       <c r="I39" t="n">
-        <v>192.7</v>
+        <v>188.05</v>
       </c>
       <c r="J39" t="n">
-        <v>194.3699999999916</v>
+        <v>189.7199999999916</v>
       </c>
       <c r="K39" t="n">
         <v>1.669999999991632</v>
       </c>
       <c r="L39" t="n">
-        <v>199.8799999999916</v>
+        <v>195.2299999999916</v>
       </c>
       <c r="M39" t="n">
-        <v>201.4</v>
+        <v>196.75</v>
       </c>
       <c r="N39" t="n">
-        <v>199.8799999999916</v>
+        <v>195.2299999999916</v>
       </c>
     </row>
     <row r="40">
@@ -2402,22 +2402,22 @@
         <v>195</v>
       </c>
       <c r="I41" t="n">
-        <v>201.15</v>
+        <v>196.5</v>
       </c>
       <c r="J41" t="n">
-        <v>201.15</v>
+        <v>196.5</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>207.66</v>
+        <v>203.01</v>
       </c>
       <c r="M41" t="n">
-        <v>210.18</v>
+        <v>205.53</v>
       </c>
       <c r="N41" t="n">
-        <v>207.66</v>
+        <v>203.01</v>
       </c>
     </row>
     <row r="42">
@@ -2450,22 +2450,22 @@
         <v>200</v>
       </c>
       <c r="I42" t="n">
-        <v>209.25</v>
+        <v>204.6</v>
       </c>
       <c r="J42" t="n">
-        <v>209.25</v>
+        <v>204.6</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>215.56</v>
+        <v>210.91</v>
       </c>
       <c r="M42" t="n">
-        <v>217.88</v>
+        <v>213.23</v>
       </c>
       <c r="N42" t="n">
-        <v>215.56</v>
+        <v>210.91</v>
       </c>
     </row>
     <row r="43">
@@ -2498,22 +2498,22 @@
         <v>205</v>
       </c>
       <c r="I43" t="n">
-        <v>214.25</v>
+        <v>209.6</v>
       </c>
       <c r="J43" t="n">
-        <v>217.8799999999966</v>
+        <v>213.2299999999966</v>
       </c>
       <c r="K43" t="n">
         <v>3.629999999996585</v>
       </c>
       <c r="L43" t="n">
-        <v>224.1899999999966</v>
+        <v>219.5399999999966</v>
       </c>
       <c r="M43" t="n">
-        <v>226.5099999999966</v>
+        <v>221.8599999999966</v>
       </c>
       <c r="N43" t="n">
-        <v>224.1899999999966</v>
+        <v>219.5399999999966</v>
       </c>
     </row>
     <row r="44">
@@ -2546,22 +2546,22 @@
         <v>210</v>
       </c>
       <c r="I44" t="n">
-        <v>217.7</v>
+        <v>213.05</v>
       </c>
       <c r="J44" t="n">
-        <v>217.7</v>
+        <v>213.05</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>224.01</v>
+        <v>219.36</v>
       </c>
       <c r="M44" t="n">
-        <v>226.33</v>
+        <v>221.68</v>
       </c>
       <c r="N44" t="n">
-        <v>224.01</v>
+        <v>219.36</v>
       </c>
     </row>
     <row r="45">
@@ -2594,22 +2594,22 @@
         <v>215</v>
       </c>
       <c r="I45" t="n">
-        <v>224.25</v>
+        <v>219.6</v>
       </c>
       <c r="J45" t="n">
-        <v>226.5099999999943</v>
+        <v>221.8599999999943</v>
       </c>
       <c r="K45" t="n">
         <v>2.259999999994335</v>
       </c>
       <c r="L45" t="n">
-        <v>232.3299999999943</v>
+        <v>227.6799999999943</v>
       </c>
       <c r="M45" t="n">
-        <v>234.1599999999943</v>
+        <v>229.5099999999943</v>
       </c>
       <c r="N45" t="n">
-        <v>232.3299999999943</v>
+        <v>227.6799999999943</v>
       </c>
     </row>
     <row r="46">
@@ -2642,22 +2642,22 @@
         <v>220</v>
       </c>
       <c r="I46" t="n">
-        <v>226.15</v>
+        <v>221.5</v>
       </c>
       <c r="J46" t="n">
-        <v>226.15</v>
+        <v>221.5</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>232</v>
+        <v>227.35</v>
       </c>
       <c r="M46" t="n">
-        <v>233.84</v>
+        <v>229.19</v>
       </c>
       <c r="N46" t="n">
-        <v>232</v>
+        <v>227.35</v>
       </c>
     </row>
     <row r="47">
@@ -2690,22 +2690,22 @@
         <v>225</v>
       </c>
       <c r="I47" t="n">
-        <v>232.7</v>
+        <v>228.05</v>
       </c>
       <c r="J47" t="n">
-        <v>232.7</v>
+        <v>228.05</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>239.01</v>
+        <v>234.36</v>
       </c>
       <c r="M47" t="n">
-        <v>241.33</v>
+        <v>236.68</v>
       </c>
       <c r="N47" t="n">
-        <v>239.01</v>
+        <v>234.36</v>
       </c>
     </row>
     <row r="48">
@@ -2882,22 +2882,22 @@
         <v>245</v>
       </c>
       <c r="I51" t="n">
-        <v>251.15</v>
+        <v>246.5</v>
       </c>
       <c r="J51" t="n">
-        <v>251.15</v>
+        <v>246.5</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>257.46</v>
+        <v>252.81</v>
       </c>
       <c r="M51" t="n">
-        <v>259.78</v>
+        <v>255.13</v>
       </c>
       <c r="N51" t="n">
-        <v>257.46</v>
+        <v>252.81</v>
       </c>
     </row>
     <row r="52">
@@ -2930,22 +2930,22 @@
         <v>250</v>
       </c>
       <c r="I52" t="n">
-        <v>256.15</v>
+        <v>251.5</v>
       </c>
       <c r="J52" t="n">
-        <v>259.779999999997</v>
+        <v>255.129999999997</v>
       </c>
       <c r="K52" t="n">
-        <v>3.629999999996983</v>
+        <v>3.629999999997011</v>
       </c>
       <c r="L52" t="n">
-        <v>265.6</v>
+        <v>260.95</v>
       </c>
       <c r="M52" t="n">
-        <v>267.4299999999969</v>
+        <v>262.779999999997</v>
       </c>
       <c r="N52" t="n">
-        <v>273.25</v>
+        <v>268.6</v>
       </c>
     </row>
     <row r="53">
@@ -2978,22 +2978,22 @@
         <v>255</v>
       </c>
       <c r="I53" t="n">
-        <v>261.15</v>
+        <v>256.5</v>
       </c>
       <c r="J53" t="n">
-        <v>267.4299999999896</v>
+        <v>262.7799999999897</v>
       </c>
       <c r="K53" t="n">
-        <v>6.279999999989627</v>
+        <v>6.279999999989684</v>
       </c>
       <c r="L53" t="n">
-        <v>273.25</v>
+        <v>268.6</v>
       </c>
       <c r="M53" t="n">
-        <v>275.0799999999896</v>
+        <v>270.4299999999897</v>
       </c>
       <c r="N53" t="n">
-        <v>273.25</v>
+        <v>268.6</v>
       </c>
     </row>
     <row r="54">
@@ -3122,22 +3122,22 @@
         <v>270</v>
       </c>
       <c r="I56" t="n">
-        <v>276.15</v>
+        <v>271.5</v>
       </c>
       <c r="J56" t="n">
-        <v>276.15</v>
+        <v>271.5</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>281.97</v>
+        <v>277.32</v>
       </c>
       <c r="M56" t="n">
-        <v>283.8</v>
+        <v>279.15</v>
       </c>
       <c r="N56" t="n">
-        <v>281.97</v>
+        <v>277.32</v>
       </c>
     </row>
     <row r="57">
@@ -3170,22 +3170,22 @@
         <v>275</v>
       </c>
       <c r="I57" t="n">
-        <v>284.25</v>
+        <v>279.6</v>
       </c>
       <c r="J57" t="n">
-        <v>284.25</v>
+        <v>279.6</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>290.76</v>
+        <v>286.11</v>
       </c>
       <c r="M57" t="n">
-        <v>293.28</v>
+        <v>288.63</v>
       </c>
       <c r="N57" t="n">
-        <v>290.76</v>
+        <v>286.11</v>
       </c>
     </row>
     <row r="58">
@@ -3218,22 +3218,22 @@
         <v>280</v>
       </c>
       <c r="I58" t="n">
-        <v>287.7</v>
+        <v>283.05</v>
       </c>
       <c r="J58" t="n">
-        <v>287.7</v>
+        <v>283.05</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>293.52</v>
+        <v>288.87</v>
       </c>
       <c r="M58" t="n">
-        <v>295.35</v>
+        <v>290.7</v>
       </c>
       <c r="N58" t="n">
-        <v>293.52</v>
+        <v>288.87</v>
       </c>
     </row>
     <row r="59">
@@ -3314,22 +3314,22 @@
         <v>290</v>
       </c>
       <c r="I60" t="n">
-        <v>296.15</v>
+        <v>291.5</v>
       </c>
       <c r="J60" t="n">
-        <v>296.15</v>
+        <v>291.5</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>302.33</v>
+        <v>297.68</v>
       </c>
       <c r="M60" t="n">
-        <v>304.51</v>
+        <v>299.86</v>
       </c>
       <c r="N60" t="n">
-        <v>302.33</v>
+        <v>297.68</v>
       </c>
     </row>
     <row r="61">
@@ -3362,22 +3362,22 @@
         <v>295</v>
       </c>
       <c r="I61" t="n">
-        <v>304.25</v>
+        <v>299.6</v>
       </c>
       <c r="J61" t="n">
-        <v>304.25</v>
+        <v>299.6</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>310.07</v>
+        <v>305.42</v>
       </c>
       <c r="M61" t="n">
-        <v>311.9</v>
+        <v>307.25</v>
       </c>
       <c r="N61" t="n">
-        <v>310.07</v>
+        <v>305.42</v>
       </c>
     </row>
     <row r="62">
@@ -3410,22 +3410,22 @@
         <v>300</v>
       </c>
       <c r="I62" t="n">
-        <v>307.7</v>
+        <v>303.05</v>
       </c>
       <c r="J62" t="n">
-        <v>307.7</v>
+        <v>303.05</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>313.52</v>
+        <v>308.87</v>
       </c>
       <c r="M62" t="n">
-        <v>315.35</v>
+        <v>310.7</v>
       </c>
       <c r="N62" t="n">
-        <v>313.52</v>
+        <v>308.87</v>
       </c>
     </row>
     <row r="63">
@@ -3506,22 +3506,22 @@
         <v>310</v>
       </c>
       <c r="I64" t="n">
-        <v>316.15</v>
+        <v>311.5</v>
       </c>
       <c r="J64" t="n">
-        <v>316.15</v>
+        <v>311.5</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>322.46</v>
+        <v>317.81</v>
       </c>
       <c r="M64" t="n">
-        <v>324.78</v>
+        <v>320.13</v>
       </c>
       <c r="N64" t="n">
-        <v>322.46</v>
+        <v>317.81</v>
       </c>
     </row>
     <row r="65">
@@ -3650,22 +3650,22 @@
         <v>325</v>
       </c>
       <c r="I67" t="n">
-        <v>331.15</v>
+        <v>326.5</v>
       </c>
       <c r="J67" t="n">
-        <v>331.15</v>
+        <v>326.5</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>336.49</v>
+        <v>331.84</v>
       </c>
       <c r="M67" t="n">
-        <v>337.82</v>
+        <v>333.17</v>
       </c>
       <c r="N67" t="n">
-        <v>336.49</v>
+        <v>331.84</v>
       </c>
     </row>
     <row r="68">
@@ -3698,22 +3698,22 @@
         <v>330</v>
       </c>
       <c r="I68" t="n">
-        <v>339.25</v>
+        <v>334.6</v>
       </c>
       <c r="J68" t="n">
-        <v>339.25</v>
+        <v>334.6</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>345.43</v>
+        <v>340.78</v>
       </c>
       <c r="M68" t="n">
-        <v>347.61</v>
+        <v>342.96</v>
       </c>
       <c r="N68" t="n">
-        <v>345.43</v>
+        <v>340.78</v>
       </c>
     </row>
     <row r="69">
@@ -3794,22 +3794,22 @@
         <v>340</v>
       </c>
       <c r="I70" t="n">
-        <v>349.25</v>
+        <v>344.6</v>
       </c>
       <c r="J70" t="n">
-        <v>349.25</v>
+        <v>344.6</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>355.56</v>
+        <v>350.91</v>
       </c>
       <c r="M70" t="n">
-        <v>357.88</v>
+        <v>353.23</v>
       </c>
       <c r="N70" t="n">
-        <v>355.56</v>
+        <v>350.91</v>
       </c>
     </row>
     <row r="71">
@@ -3938,22 +3938,22 @@
         <v>355</v>
       </c>
       <c r="I73" t="n">
-        <v>364.25</v>
+        <v>359.6</v>
       </c>
       <c r="J73" t="n">
-        <v>364.25</v>
+        <v>359.6</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>370.76</v>
+        <v>366.11</v>
       </c>
       <c r="M73" t="n">
-        <v>373.28</v>
+        <v>368.63</v>
       </c>
       <c r="N73" t="n">
-        <v>370.76</v>
+        <v>366.11</v>
       </c>
     </row>
     <row r="74">
@@ -4034,22 +4034,22 @@
         <v>365</v>
       </c>
       <c r="I75" t="n">
-        <v>372.7</v>
+        <v>368.05</v>
       </c>
       <c r="J75" t="n">
-        <v>372.7</v>
+        <v>368.05</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>379.01</v>
+        <v>374.36</v>
       </c>
       <c r="M75" t="n">
-        <v>381.33</v>
+        <v>376.68</v>
       </c>
       <c r="N75" t="n">
-        <v>379.01</v>
+        <v>374.36</v>
       </c>
     </row>
     <row r="76">
@@ -4082,22 +4082,22 @@
         <v>370</v>
       </c>
       <c r="I76" t="n">
-        <v>376.15</v>
+        <v>371.5</v>
       </c>
       <c r="J76" t="n">
-        <v>376.15</v>
+        <v>371.5</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>382.33</v>
+        <v>377.68</v>
       </c>
       <c r="M76" t="n">
-        <v>384.51</v>
+        <v>379.86</v>
       </c>
       <c r="N76" t="n">
-        <v>382.33</v>
+        <v>377.68</v>
       </c>
     </row>
     <row r="77">
@@ -4130,22 +4130,22 @@
         <v>375</v>
       </c>
       <c r="I77" t="n">
-        <v>384.25</v>
+        <v>379.6</v>
       </c>
       <c r="J77" t="n">
-        <v>384.25</v>
+        <v>379.6</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>390.43</v>
+        <v>385.78</v>
       </c>
       <c r="M77" t="n">
-        <v>392.61</v>
+        <v>387.96</v>
       </c>
       <c r="N77" t="n">
-        <v>390.43</v>
+        <v>385.78</v>
       </c>
     </row>
     <row r="78">
@@ -4178,22 +4178,22 @@
         <v>380</v>
       </c>
       <c r="I78" t="n">
-        <v>389.25</v>
+        <v>384.6</v>
       </c>
       <c r="J78" t="n">
-        <v>392.6099999999969</v>
+        <v>387.959999999997</v>
       </c>
       <c r="K78" t="n">
         <v>3.359999999996944</v>
       </c>
       <c r="L78" t="n">
-        <v>399.1199999999969</v>
+        <v>394.469999999997</v>
       </c>
       <c r="M78" t="n">
-        <v>401.6399999999969</v>
+        <v>396.9899999999969</v>
       </c>
       <c r="N78" t="n">
-        <v>399.1199999999969</v>
+        <v>394.469999999997</v>
       </c>
     </row>
     <row r="79">
@@ -4322,22 +4322,22 @@
         <v>395</v>
       </c>
       <c r="I81" t="n">
-        <v>404.25</v>
+        <v>399.6</v>
       </c>
       <c r="J81" t="n">
-        <v>404.25</v>
+        <v>399.6</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>409.76</v>
+        <v>405.11</v>
       </c>
       <c r="M81" t="n">
-        <v>411.28</v>
+        <v>406.63</v>
       </c>
       <c r="N81" t="n">
-        <v>409.76</v>
+        <v>405.11</v>
       </c>
     </row>
     <row r="82">
@@ -4370,22 +4370,22 @@
         <v>400</v>
       </c>
       <c r="I82" t="n">
-        <v>407.7</v>
+        <v>403.05</v>
       </c>
       <c r="J82" t="n">
-        <v>407.7</v>
+        <v>403.05</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>414.21</v>
+        <v>409.56</v>
       </c>
       <c r="M82" t="n">
-        <v>416.73</v>
+        <v>412.08</v>
       </c>
       <c r="N82" t="n">
-        <v>414.21</v>
+        <v>409.56</v>
       </c>
     </row>
     <row r="83">
@@ -4466,22 +4466,22 @@
         <v>410</v>
       </c>
       <c r="I84" t="n">
-        <v>417.7</v>
+        <v>413.05</v>
       </c>
       <c r="J84" t="n">
-        <v>417.7</v>
+        <v>413.05</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>423.88</v>
+        <v>419.23</v>
       </c>
       <c r="M84" t="n">
-        <v>426.06</v>
+        <v>421.41</v>
       </c>
       <c r="N84" t="n">
-        <v>423.88</v>
+        <v>419.23</v>
       </c>
     </row>
     <row r="85">
@@ -4514,22 +4514,22 @@
         <v>415</v>
       </c>
       <c r="I85" t="n">
-        <v>422.7</v>
+        <v>418.05</v>
       </c>
       <c r="J85" t="n">
-        <v>426.0599999999969</v>
+        <v>421.409999999997</v>
       </c>
       <c r="K85" t="n">
         <v>3.359999999996944</v>
       </c>
       <c r="L85" t="n">
-        <v>432.5699999999969</v>
+        <v>427.9199999999969</v>
       </c>
       <c r="M85" t="n">
-        <v>435.089999999997</v>
+        <v>430.439999999997</v>
       </c>
       <c r="N85" t="n">
-        <v>432.5699999999969</v>
+        <v>427.9199999999969</v>
       </c>
     </row>
     <row r="86">
@@ -4562,22 +4562,22 @@
         <v>420</v>
       </c>
       <c r="I86" t="n">
-        <v>429.25</v>
+        <v>424.6</v>
       </c>
       <c r="J86" t="n">
-        <v>429.25</v>
+        <v>424.6</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>435.56</v>
+        <v>430.91</v>
       </c>
       <c r="M86" t="n">
-        <v>437.88</v>
+        <v>433.23</v>
       </c>
       <c r="N86" t="n">
-        <v>435.56</v>
+        <v>430.91</v>
       </c>
     </row>
     <row r="87">
@@ -4658,22 +4658,22 @@
         <v>430</v>
       </c>
       <c r="I88" t="n">
-        <v>437.7</v>
+        <v>433.05</v>
       </c>
       <c r="J88" t="n">
-        <v>437.7</v>
+        <v>433.05</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>443.88</v>
+        <v>439.23</v>
       </c>
       <c r="M88" t="n">
-        <v>446.06</v>
+        <v>441.41</v>
       </c>
       <c r="N88" t="n">
-        <v>443.88</v>
+        <v>439.23</v>
       </c>
     </row>
     <row r="89">
@@ -4754,22 +4754,22 @@
         <v>440</v>
       </c>
       <c r="I90" t="n">
-        <v>449.25</v>
+        <v>444.6</v>
       </c>
       <c r="J90" t="n">
-        <v>449.25</v>
+        <v>444.6</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>455.1</v>
+        <v>450.45</v>
       </c>
       <c r="M90" t="n">
-        <v>456.94</v>
+        <v>452.29</v>
       </c>
       <c r="N90" t="n">
-        <v>502.7899999999951</v>
+        <v>498.1399999999951</v>
       </c>
     </row>
     <row r="91">
@@ -4946,22 +4946,22 @@
         <v>460</v>
       </c>
       <c r="I94" t="n">
-        <v>466.15</v>
+        <v>461.5</v>
       </c>
       <c r="J94" t="n">
-        <v>466.15</v>
+        <v>461.5</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>471.66</v>
+        <v>467.01</v>
       </c>
       <c r="M94" t="n">
-        <v>473.1799999999999</v>
+        <v>468.53</v>
       </c>
       <c r="N94" t="n">
-        <v>506.66</v>
+        <v>502.01</v>
       </c>
     </row>
     <row r="95">
@@ -4994,22 +4994,22 @@
         <v>465</v>
       </c>
       <c r="I95" t="n">
-        <v>472.7</v>
+        <v>468.05</v>
       </c>
       <c r="J95" t="n">
-        <v>472.7</v>
+        <v>468.05</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>479.01</v>
+        <v>474.36</v>
       </c>
       <c r="M95" t="n">
-        <v>481.33</v>
+        <v>476.68</v>
       </c>
       <c r="N95" t="n">
-        <v>514.01</v>
+        <v>509.36</v>
       </c>
     </row>
     <row r="96">
@@ -5042,22 +5042,22 @@
         <v>470</v>
       </c>
       <c r="I96" t="n">
-        <v>479.25</v>
+        <v>474.6</v>
       </c>
       <c r="J96" t="n">
-        <v>479.25</v>
+        <v>474.6</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>485.1</v>
+        <v>480.45</v>
       </c>
       <c r="M96" t="n">
-        <v>486.94</v>
+        <v>482.29</v>
       </c>
       <c r="N96" t="n">
-        <v>502.7899999999951</v>
+        <v>498.1399999999951</v>
       </c>
     </row>
     <row r="97">
@@ -5138,22 +5138,22 @@
         <v>480</v>
       </c>
       <c r="I98" t="n">
-        <v>489.25</v>
+        <v>484.6</v>
       </c>
       <c r="J98" t="n">
-        <v>489.25</v>
+        <v>484.6</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>495.1</v>
+        <v>490.45</v>
       </c>
       <c r="M98" t="n">
-        <v>496.94</v>
+        <v>492.29</v>
       </c>
       <c r="N98" t="n">
-        <v>502.7899999999951</v>
+        <v>498.1399999999951</v>
       </c>
     </row>
     <row r="99">
@@ -5186,22 +5186,22 @@
         <v>485</v>
       </c>
       <c r="I99" t="n">
-        <v>494.25</v>
+        <v>489.6</v>
       </c>
       <c r="J99" t="n">
-        <v>496.9399999999951</v>
+        <v>492.2899999999951</v>
       </c>
       <c r="K99" t="n">
         <v>2.689999999995052</v>
       </c>
       <c r="L99" t="n">
-        <v>502.7899999999951</v>
+        <v>498.1399999999951</v>
       </c>
       <c r="M99" t="n">
-        <v>504.6299999999951</v>
+        <v>499.9799999999951</v>
       </c>
       <c r="N99" t="n">
-        <v>502.7899999999951</v>
+        <v>498.1399999999951</v>
       </c>
     </row>
     <row r="100">
@@ -5282,22 +5282,22 @@
         <v>495</v>
       </c>
       <c r="I101" t="n">
-        <v>501.15</v>
+        <v>496.5</v>
       </c>
       <c r="J101" t="n">
-        <v>501.15</v>
+        <v>496.5</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>506.66</v>
+        <v>502.01</v>
       </c>
       <c r="M101" t="n">
-        <v>508.1799999999999</v>
+        <v>503.53</v>
       </c>
       <c r="N101" t="n">
-        <v>506.66</v>
+        <v>502.01</v>
       </c>
     </row>
     <row r="102">
@@ -5330,22 +5330,22 @@
         <v>500</v>
       </c>
       <c r="I102" t="n">
-        <v>507.7</v>
+        <v>503.05</v>
       </c>
       <c r="J102" t="n">
-        <v>507.7</v>
+        <v>503.05</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>514.01</v>
+        <v>509.36</v>
       </c>
       <c r="M102" t="n">
-        <v>516.33</v>
+        <v>511.68</v>
       </c>
       <c r="N102" t="n">
-        <v>514.01</v>
+        <v>509.36</v>
       </c>
     </row>
     <row r="103">

--- a/MIP_RULE/results/random_best_piece_details.xlsx
+++ b/MIP_RULE/results/random_best_piece_details.xlsx
@@ -1016,7 +1016,7 @@
         <v>57.25</v>
       </c>
       <c r="K12" t="n">
-        <v>2.649999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="L12" t="n">
         <v>63.42999999999656</v>
